--- a/fat.xlsx
+++ b/fat.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b5c92e1b1a667af/Área de Trabalho/faturamento/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81558D05-BE6A-4B33-9D46-E77397144D81}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{D991FB55-A98B-4966-87EA-837A1BBDE054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8F28E26-9E57-4D80-9E15-ABB796B6DC1B}"/>
   <bookViews>
-    <workbookView xWindow="-23400" yWindow="600" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20790" yWindow="930" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FATURAMENTO Á RECEBER" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$1195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FATURAMENTO Á RECEBER'!$A$1:$G$1347</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3589" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4045" uniqueCount="280">
   <si>
     <t>Gerador</t>
   </si>
@@ -875,6 +875,9 @@
   <si>
     <t>REG AGRO | COLINA</t>
   </si>
+  <si>
+    <t>CFX ENGENHARIA</t>
+  </si>
 </sst>
 </file>
 
@@ -1280,7 +1283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:G1195"/>
+  <dimension ref="A1:G1347"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" style="4" bestFit="1" customWidth="1"/>
@@ -25976,7 +25979,7 @@
         <v>0.08</v>
       </c>
       <c r="G1029" s="2">
-        <f t="shared" ref="G1029:G1195" si="15">E1029*F1029</f>
+        <f t="shared" ref="G1029:G1285" si="15">E1029*F1029</f>
         <v>43.188800000000001</v>
       </c>
     </row>
@@ -26316,7 +26319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1044" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1044" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1044" s="3" t="s">
         <v>4</v>
       </c>
@@ -26340,7 +26343,7 @@
         <v>68.314999999999998</v>
       </c>
     </row>
-    <row r="1045" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1045" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1045" s="3" t="s">
         <v>4</v>
       </c>
@@ -26364,7 +26367,7 @@
         <v>341.56799999999998</v>
       </c>
     </row>
-    <row r="1046" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1046" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1046" s="3" t="s">
         <v>4</v>
       </c>
@@ -26388,7 +26391,7 @@
         <v>16.64</v>
       </c>
     </row>
-    <row r="1047" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1047" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1047" s="3" t="s">
         <v>4</v>
       </c>
@@ -26412,7 +26415,7 @@
         <v>613.82399999999996</v>
       </c>
     </row>
-    <row r="1048" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1048" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1048" s="3" t="s">
         <v>4</v>
       </c>
@@ -26436,7 +26439,7 @@
         <v>12.544</v>
       </c>
     </row>
-    <row r="1049" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1049" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1049" s="3" t="s">
         <v>4</v>
       </c>
@@ -26460,7 +26463,7 @@
         <v>171.78900000000002</v>
       </c>
     </row>
-    <row r="1050" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1050" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1050" s="3" t="s">
         <v>4</v>
       </c>
@@ -26484,7 +26487,7 @@
         <v>29.183999999999997</v>
       </c>
     </row>
-    <row r="1051" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1051" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1051" s="3" t="s">
         <v>4</v>
       </c>
@@ -26508,7 +26511,7 @@
         <v>138.11500000000001</v>
       </c>
     </row>
-    <row r="1052" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1052" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1052" s="3" t="s">
         <v>4</v>
       </c>
@@ -26532,7 +26535,7 @@
         <v>1119.8720000000001</v>
       </c>
     </row>
-    <row r="1053" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1053" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1053" s="3" t="s">
         <v>4</v>
       </c>
@@ -26556,7 +26559,7 @@
         <v>36.927</v>
       </c>
     </row>
-    <row r="1054" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1054" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1054" s="3" t="s">
         <v>4</v>
       </c>
@@ -26580,7 +26583,7 @@
         <v>55.910000000000004</v>
       </c>
     </row>
-    <row r="1055" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1055" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1055" s="3" t="s">
         <v>27</v>
       </c>
@@ -26604,7 +26607,7 @@
         <v>1166.1320000000001</v>
       </c>
     </row>
-    <row r="1056" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1056" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1056" s="3" t="s">
         <v>31</v>
       </c>
@@ -26628,7 +26631,7 @@
         <v>543.18079999999998</v>
       </c>
     </row>
-    <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1057" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1057" s="3" t="s">
         <v>31</v>
       </c>
@@ -26652,7 +26655,7 @@
         <v>502.93760000000003</v>
       </c>
     </row>
-    <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1058" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1058" s="3" t="s">
         <v>31</v>
       </c>
@@ -26676,7 +26679,7 @@
         <v>212.07040000000001</v>
       </c>
     </row>
-    <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1059" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1059" s="3" t="s">
         <v>31</v>
       </c>
@@ -26700,7 +26703,7 @@
         <v>132.81280000000001</v>
       </c>
     </row>
-    <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1060" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1060" s="3" t="s">
         <v>31</v>
       </c>
@@ -26724,7 +26727,7 @@
         <v>168.08959999999999</v>
       </c>
     </row>
-    <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1061" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1061" s="3" t="s">
         <v>31</v>
       </c>
@@ -26748,7 +26751,7 @@
         <v>148.3776</v>
       </c>
     </row>
-    <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1062" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1062" s="3" t="s">
         <v>31</v>
       </c>
@@ -26772,7 +26775,7 @@
         <v>191.54240000000001</v>
       </c>
     </row>
-    <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1063" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1063" s="3" t="s">
         <v>31</v>
       </c>
@@ -26796,7 +26799,7 @@
         <v>219.06880000000001</v>
       </c>
     </row>
-    <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1064" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1064" s="3" t="s">
         <v>31</v>
       </c>
@@ -26820,7 +26823,7 @@
         <v>380.41919999999999</v>
       </c>
     </row>
-    <row r="1065" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1065" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1065" s="3" t="s">
         <v>31</v>
       </c>
@@ -26844,7 +26847,7 @@
         <v>192.24</v>
       </c>
     </row>
-    <row r="1066" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1066" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1066" s="3" t="s">
         <v>31</v>
       </c>
@@ -26868,7 +26871,7 @@
         <v>56.601599999999998</v>
       </c>
     </row>
-    <row r="1067" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1067" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1067" s="3" t="s">
         <v>31</v>
       </c>
@@ -26892,7 +26895,7 @@
         <v>41.078400000000002</v>
       </c>
     </row>
-    <row r="1068" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1068" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1068" s="3" t="s">
         <v>31</v>
       </c>
@@ -26916,7 +26919,7 @@
         <v>106.85520000000001</v>
       </c>
     </row>
-    <row r="1069" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1069" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1069" s="3" t="s">
         <v>31</v>
       </c>
@@ -26940,7 +26943,7 @@
         <v>31.468800000000002</v>
       </c>
     </row>
-    <row r="1070" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1070" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1070" s="3" t="s">
         <v>31</v>
       </c>
@@ -26964,7 +26967,7 @@
         <v>101.7872</v>
       </c>
     </row>
-    <row r="1071" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1071" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1071" s="3" t="s">
         <v>31</v>
       </c>
@@ -26988,7 +26991,7 @@
         <v>106.39200000000001</v>
       </c>
     </row>
-    <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1072" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1072" s="3" t="s">
         <v>31</v>
       </c>
@@ -27012,7 +27015,7 @@
         <v>22.619200000000003</v>
       </c>
     </row>
-    <row r="1073" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1073" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1073" s="3" t="s">
         <v>31</v>
       </c>
@@ -27036,7 +27039,7 @@
         <v>11.684800000000001</v>
       </c>
     </row>
-    <row r="1074" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1074" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1074" s="3" t="s">
         <v>31</v>
       </c>
@@ -27060,7 +27063,7 @@
         <v>37.527200000000001</v>
       </c>
     </row>
-    <row r="1075" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1075" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1075" s="3" t="s">
         <v>31</v>
       </c>
@@ -27084,7 +27087,7 @@
         <v>25.189600000000002</v>
       </c>
     </row>
-    <row r="1076" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1076" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1076" s="3" t="s">
         <v>31</v>
       </c>
@@ -27108,7 +27111,7 @@
         <v>23.7608</v>
       </c>
     </row>
-    <row r="1077" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1077" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1077" s="3" t="s">
         <v>31</v>
       </c>
@@ -27132,7 +27135,7 @@
         <v>24.066399999999998</v>
       </c>
     </row>
-    <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1078" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1078" s="3" t="s">
         <v>31</v>
       </c>
@@ -27156,7 +27159,7 @@
         <v>65.606400000000008</v>
       </c>
     </row>
-    <row r="1079" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1079" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1079" s="3" t="s">
         <v>31</v>
       </c>
@@ -27180,7 +27183,7 @@
         <v>48.025600000000004</v>
       </c>
     </row>
-    <row r="1080" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1080" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1080" s="3" t="s">
         <v>31</v>
       </c>
@@ -27204,7 +27207,7 @@
         <v>114.7872</v>
       </c>
     </row>
-    <row r="1081" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1081" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1081" s="3" t="s">
         <v>31</v>
       </c>
@@ -27228,7 +27231,7 @@
         <v>94.670400000000015</v>
       </c>
     </row>
-    <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1082" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1082" s="3" t="s">
         <v>60</v>
       </c>
@@ -27252,7 +27255,7 @@
         <v>225.245</v>
       </c>
     </row>
-    <row r="1083" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1083" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1083" s="3" t="s">
         <v>60</v>
       </c>
@@ -27276,7 +27279,7 @@
         <v>137.215</v>
       </c>
     </row>
-    <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1084" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1084" s="3" t="s">
         <v>60</v>
       </c>
@@ -27300,7 +27303,7 @@
         <v>166.16600000000003</v>
       </c>
     </row>
-    <row r="1085" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1085" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1085" s="3" t="s">
         <v>60</v>
       </c>
@@ -27324,7 +27327,7 @@
         <v>144.44800000000001</v>
       </c>
     </row>
-    <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1086" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1086" s="3" t="s">
         <v>60</v>
       </c>
@@ -27348,7 +27351,7 @@
         <v>114.336</v>
       </c>
     </row>
-    <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1087" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1087" s="3" t="s">
         <v>60</v>
       </c>
@@ -27372,7 +27375,7 @@
         <v>131.60050000000001</v>
       </c>
     </row>
-    <row r="1088" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1088" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1088" s="3" t="s">
         <v>60</v>
       </c>
@@ -27396,7 +27399,7 @@
         <v>101.952</v>
       </c>
     </row>
-    <row r="1089" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1089" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1089" s="3" t="s">
         <v>60</v>
       </c>
@@ -27420,7 +27423,7 @@
         <v>98.215000000000003</v>
       </c>
     </row>
-    <row r="1090" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1090" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1090" s="3" t="s">
         <v>60</v>
       </c>
@@ -27444,7 +27447,7 @@
         <v>215.78700000000001</v>
       </c>
     </row>
-    <row r="1091" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1091" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1091" s="3" t="s">
         <v>60</v>
       </c>
@@ -27468,7 +27471,7 @@
         <v>485.84799999999996</v>
       </c>
     </row>
-    <row r="1092" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1092" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1092" s="3" t="s">
         <v>60</v>
       </c>
@@ -27492,7 +27495,7 @@
         <v>612.12800000000004</v>
       </c>
     </row>
-    <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1093" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1093" s="3" t="s">
         <v>60</v>
       </c>
@@ -27516,7 +27519,7 @@
         <v>245.92</v>
       </c>
     </row>
-    <row r="1094" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1094" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1094" s="3" t="s">
         <v>60</v>
       </c>
@@ -27540,7 +27543,7 @@
         <v>450.19</v>
       </c>
     </row>
-    <row r="1095" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1095" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1095" s="3" t="s">
         <v>60</v>
       </c>
@@ -27564,7 +27567,7 @@
         <v>152.54749999999999</v>
       </c>
     </row>
-    <row r="1096" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1096" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1096" s="3" t="s">
         <v>60</v>
       </c>
@@ -27588,7 +27591,7 @@
         <v>43.127499999999998</v>
       </c>
     </row>
-    <row r="1097" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1097" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1097" s="3" t="s">
         <v>60</v>
       </c>
@@ -27612,7 +27615,7 @@
         <v>262.66399999999999</v>
       </c>
     </row>
-    <row r="1098" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1098" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1098" s="3" t="s">
         <v>60</v>
       </c>
@@ -27636,7 +27639,7 @@
         <v>196.755</v>
       </c>
     </row>
-    <row r="1099" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1099" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1099" s="3" t="s">
         <v>60</v>
       </c>
@@ -27660,7 +27663,7 @@
         <v>29.727999999999998</v>
       </c>
     </row>
-    <row r="1100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1100" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1100" s="3" t="s">
         <v>60</v>
       </c>
@@ -27684,7 +27687,7 @@
         <v>272.76799999999997</v>
       </c>
     </row>
-    <row r="1101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1101" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1101" s="3" t="s">
         <v>60</v>
       </c>
@@ -27708,7 +27711,7 @@
         <v>478.59200000000004</v>
       </c>
     </row>
-    <row r="1102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1102" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1102" s="3" t="s">
         <v>60</v>
       </c>
@@ -27732,7 +27735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1103" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1103" s="3" t="s">
         <v>60</v>
       </c>
@@ -27756,7 +27759,7 @@
         <v>3.0720000000000001</v>
       </c>
     </row>
-    <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1104" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1104" s="3" t="s">
         <v>60</v>
       </c>
@@ -27780,7 +27783,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="1105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1105" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1105" s="3" t="s">
         <v>60</v>
       </c>
@@ -27804,7 +27807,7 @@
         <v>248.74699999999999</v>
       </c>
     </row>
-    <row r="1106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1106" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1106" s="3" t="s">
         <v>60</v>
       </c>
@@ -27828,7 +27831,7 @@
         <v>252.608</v>
       </c>
     </row>
-    <row r="1107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1107" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1107" s="3" t="s">
         <v>60</v>
       </c>
@@ -27852,7 +27855,7 @@
         <v>360.73600000000005</v>
       </c>
     </row>
-    <row r="1108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1108" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1108" s="3" t="s">
         <v>60</v>
       </c>
@@ -27876,7 +27879,7 @@
         <v>361.46500000000003</v>
       </c>
     </row>
-    <row r="1109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1109" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1109" s="3" t="s">
         <v>60</v>
       </c>
@@ -27900,7 +27903,7 @@
         <v>361.46500000000003</v>
       </c>
     </row>
-    <row r="1110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1110" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1110" s="3" t="s">
         <v>99</v>
       </c>
@@ -27924,7 +27927,7 @@
         <v>428.68080000000003</v>
       </c>
     </row>
-    <row r="1111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1111" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1111" s="3" t="s">
         <v>99</v>
       </c>
@@ -27948,7 +27951,7 @@
         <v>26.003200000000003</v>
       </c>
     </row>
-    <row r="1112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1112" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1112" s="3" t="s">
         <v>99</v>
       </c>
@@ -27972,7 +27975,7 @@
         <v>23.241599999999998</v>
       </c>
     </row>
-    <row r="1113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1113" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1113" s="3" t="s">
         <v>99</v>
       </c>
@@ -27996,7 +27999,7 @@
         <v>46.180799999999998</v>
       </c>
     </row>
-    <row r="1114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1114" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1114" s="3" t="s">
         <v>99</v>
       </c>
@@ -28020,7 +28023,7 @@
         <v>18.014400000000002</v>
       </c>
     </row>
-    <row r="1115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1115" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1115" s="3" t="s">
         <v>99</v>
       </c>
@@ -28044,7 +28047,7 @@
         <v>117.5984</v>
       </c>
     </row>
-    <row r="1116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1116" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1116" s="3" t="s">
         <v>99</v>
       </c>
@@ -28068,7 +28071,7 @@
         <v>89.76</v>
       </c>
     </row>
-    <row r="1117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1117" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1117" s="3" t="s">
         <v>99</v>
       </c>
@@ -28092,7 +28095,7 @@
         <v>341.45279999999997</v>
       </c>
     </row>
-    <row r="1118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1118" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1118" s="3" t="s">
         <v>99</v>
       </c>
@@ -28116,7 +28119,7 @@
         <v>101.11200000000001</v>
       </c>
     </row>
-    <row r="1119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1119" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1119" s="3" t="s">
         <v>99</v>
       </c>
@@ -28140,7 +28143,7 @@
         <v>53.169600000000003</v>
       </c>
     </row>
-    <row r="1120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1120" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1120" s="3" t="s">
         <v>99</v>
       </c>
@@ -28164,7 +28167,7 @@
         <v>544.83839999999998</v>
       </c>
     </row>
-    <row r="1121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1121" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1121" s="3" t="s">
         <v>99</v>
       </c>
@@ -28188,7 +28191,7 @@
         <v>804.57759999999996</v>
       </c>
     </row>
-    <row r="1122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1122" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1122" s="3" t="s">
         <v>99</v>
       </c>
@@ -28212,7 +28215,7 @@
         <v>26.4192</v>
       </c>
     </row>
-    <row r="1123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1123" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1123" s="3" t="s">
         <v>99</v>
       </c>
@@ -28236,7 +28239,7 @@
         <v>426.66</v>
       </c>
     </row>
-    <row r="1124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1124" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1124" s="3" t="s">
         <v>99</v>
       </c>
@@ -28260,7 +28263,7 @@
         <v>209.50800000000001</v>
       </c>
     </row>
-    <row r="1125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1125" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1125" s="3" t="s">
         <v>99</v>
       </c>
@@ -28284,7 +28287,7 @@
         <v>447.59839999999997</v>
       </c>
     </row>
-    <row r="1126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1126" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1126" s="3" t="s">
         <v>99</v>
       </c>
@@ -28308,7 +28311,7 @@
         <v>351.02719999999999</v>
       </c>
     </row>
-    <row r="1127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1127" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1127" s="3" t="s">
         <v>99</v>
       </c>
@@ -28332,7 +28335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1128" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1128" s="3" t="s">
         <v>99</v>
       </c>
@@ -28356,7 +28359,7 @@
         <v>221.65520000000001</v>
       </c>
     </row>
-    <row r="1129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1129" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1129" s="3" t="s">
         <v>99</v>
       </c>
@@ -28380,7 +28383,7 @@
         <v>17.305599999999998</v>
       </c>
     </row>
-    <row r="1130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1130" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1130" s="3" t="s">
         <v>99</v>
       </c>
@@ -28404,7 +28407,7 @@
         <v>205.8048</v>
       </c>
     </row>
-    <row r="1131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1131" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1131" s="3" t="s">
         <v>99</v>
       </c>
@@ -28428,7 +28431,7 @@
         <v>510.62400000000002</v>
       </c>
     </row>
-    <row r="1132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1132" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1132" s="3" t="s">
         <v>99</v>
       </c>
@@ -28452,7 +28455,7 @@
         <v>53.2224</v>
       </c>
     </row>
-    <row r="1133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1133" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1133" s="3" t="s">
         <v>99</v>
       </c>
@@ -28476,7 +28479,7 @@
         <v>452.30080000000004</v>
       </c>
     </row>
-    <row r="1134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1134" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1134" s="3" t="s">
         <v>99</v>
       </c>
@@ -28500,7 +28503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1135" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1135" s="3" t="s">
         <v>99</v>
       </c>
@@ -28524,7 +28527,7 @@
         <v>126.75200000000001</v>
       </c>
     </row>
-    <row r="1136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1136" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1136" s="3" t="s">
         <v>99</v>
       </c>
@@ -28548,7 +28551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1137" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1137" s="3" t="s">
         <v>99</v>
       </c>
@@ -28572,7 +28575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1138" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1138" s="3" t="s">
         <v>129</v>
       </c>
@@ -28596,7 +28599,7 @@
         <v>173.77200000000002</v>
       </c>
     </row>
-    <row r="1139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1139" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1139" s="3" t="s">
         <v>129</v>
       </c>
@@ -28620,7 +28623,7 @@
         <v>122.64300000000001</v>
       </c>
     </row>
-    <row r="1140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1140" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1140" s="3" t="s">
         <v>129</v>
       </c>
@@ -28644,7 +28647,7 @@
         <v>504.09</v>
       </c>
     </row>
-    <row r="1141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1141" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1141" s="3" t="s">
         <v>129</v>
       </c>
@@ -28668,7 +28671,7 @@
         <v>10.638</v>
       </c>
     </row>
-    <row r="1142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1142" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1142" s="3" t="s">
         <v>129</v>
       </c>
@@ -28692,7 +28695,7 @@
         <v>320.25600000000003</v>
       </c>
     </row>
-    <row r="1143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1143" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1143" s="3" t="s">
         <v>129</v>
       </c>
@@ -28716,7 +28719,7 @@
         <v>680.55000000000007</v>
       </c>
     </row>
-    <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1144" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1144" s="3" t="s">
         <v>129</v>
       </c>
@@ -28740,7 +28743,7 @@
         <v>61.376000000000005</v>
       </c>
     </row>
-    <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1145" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1145" s="3" t="s">
         <v>129</v>
       </c>
@@ -28764,7 +28767,7 @@
         <v>93.567999999999998</v>
       </c>
     </row>
-    <row r="1146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1146" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1146" s="3" t="s">
         <v>129</v>
       </c>
@@ -28788,7 +28791,7 @@
         <v>150.08000000000001</v>
       </c>
     </row>
-    <row r="1147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1147" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1147" s="3" t="s">
         <v>129</v>
       </c>
@@ -28812,7 +28815,7 @@
         <v>142.78399999999999</v>
       </c>
     </row>
-    <row r="1148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1148" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1148" s="3" t="s">
         <v>129</v>
       </c>
@@ -28836,7 +28839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1149" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1149" s="3" t="s">
         <v>277</v>
       </c>
@@ -28860,7 +28863,7 @@
         <v>312.51</v>
       </c>
     </row>
-    <row r="1150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1150" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1150" s="3" t="s">
         <v>277</v>
       </c>
@@ -28884,7 +28887,7 @@
         <v>662.40000000000009</v>
       </c>
     </row>
-    <row r="1151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1151" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1151" s="3" t="s">
         <v>277</v>
       </c>
@@ -28908,7 +28911,7 @@
         <v>293.40000000000003</v>
       </c>
     </row>
-    <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1152" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1152" s="3" t="s">
         <v>277</v>
       </c>
@@ -28932,7 +28935,7 @@
         <v>956.12199999999996</v>
       </c>
     </row>
-    <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1153" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1153" s="3" t="s">
         <v>277</v>
       </c>
@@ -28956,7 +28959,7 @@
         <v>644.30000000000007</v>
       </c>
     </row>
-    <row r="1154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1154" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1154" s="3" t="s">
         <v>168</v>
       </c>
@@ -28980,7 +28983,7 @@
         <v>126.91800000000001</v>
       </c>
     </row>
-    <row r="1155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1155" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1155" s="3" t="s">
         <v>168</v>
       </c>
@@ -29004,7 +29007,7 @@
         <v>141.17400000000001</v>
       </c>
     </row>
-    <row r="1156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1156" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1156" s="3" t="s">
         <v>168</v>
       </c>
@@ -29028,7 +29031,7 @@
         <v>216.69000000000003</v>
       </c>
     </row>
-    <row r="1157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1157" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1157" s="3" t="s">
         <v>168</v>
       </c>
@@ -29052,7 +29055,7 @@
         <v>265.42199999999997</v>
       </c>
     </row>
-    <row r="1158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1158" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1158" s="3" t="s">
         <v>154</v>
       </c>
@@ -29076,7 +29079,7 @@
         <v>408.17700000000002</v>
       </c>
     </row>
-    <row r="1159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1159" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1159" s="3" t="s">
         <v>154</v>
       </c>
@@ -29100,7 +29103,7 @@
         <v>249.08400000000003</v>
       </c>
     </row>
-    <row r="1160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1160" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1160" s="3" t="s">
         <v>154</v>
       </c>
@@ -29124,7 +29127,7 @@
         <v>444.90600000000006</v>
       </c>
     </row>
-    <row r="1161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1161" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1161" s="3" t="s">
         <v>154</v>
       </c>
@@ -29148,7 +29151,7 @@
         <v>347.58400000000006</v>
       </c>
     </row>
-    <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1162" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1162" s="3" t="s">
         <v>154</v>
       </c>
@@ -29172,7 +29175,7 @@
         <v>20.856000000000002</v>
       </c>
     </row>
-    <row r="1163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1163" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1163" s="3" t="s">
         <v>154</v>
       </c>
@@ -29196,7 +29199,7 @@
         <v>675.33699999999999</v>
       </c>
     </row>
-    <row r="1164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1164" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1164" s="3" t="s">
         <v>154</v>
       </c>
@@ -29220,7 +29223,7 @@
         <v>1295.5140000000001</v>
       </c>
     </row>
-    <row r="1165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1165" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1165" s="3" t="s">
         <v>154</v>
       </c>
@@ -29244,7 +29247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1166" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1166" s="3" t="s">
         <v>169</v>
       </c>
@@ -29268,7 +29271,7 @@
         <v>128.535</v>
       </c>
     </row>
-    <row r="1167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1167" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1167" s="3" t="s">
         <v>169</v>
       </c>
@@ -29292,7 +29295,7 @@
         <v>370.04</v>
       </c>
     </row>
-    <row r="1168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1168" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1168" s="3" t="s">
         <v>176</v>
       </c>
@@ -29316,7 +29319,7 @@
         <v>296.142</v>
       </c>
     </row>
-    <row r="1169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1169" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1169" s="3" t="s">
         <v>176</v>
       </c>
@@ -29340,7 +29343,7 @@
         <v>620.42000000000007</v>
       </c>
     </row>
-    <row r="1170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1170" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1170" s="3" t="s">
         <v>176</v>
       </c>
@@ -29364,7 +29367,7 @@
         <v>126.4</v>
       </c>
     </row>
-    <row r="1171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1171" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1171" s="3" t="s">
         <v>176</v>
       </c>
@@ -29388,7 +29391,7 @@
         <v>343.36</v>
       </c>
     </row>
-    <row r="1172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1172" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1172" s="3" t="s">
         <v>176</v>
       </c>
@@ -29412,7 +29415,7 @@
         <v>212.864</v>
       </c>
     </row>
-    <row r="1173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1173" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1173" s="3" t="s">
         <v>179</v>
       </c>
@@ -29436,7 +29439,7 @@
         <v>87.490000000000009</v>
       </c>
     </row>
-    <row r="1174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1174" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1174" s="3" t="s">
         <v>181</v>
       </c>
@@ -29460,7 +29463,7 @@
         <v>66.650000000000006</v>
       </c>
     </row>
-    <row r="1175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1175" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1175" s="3" t="s">
         <v>181</v>
       </c>
@@ -29484,7 +29487,7 @@
         <v>50.468000000000004</v>
       </c>
     </row>
-    <row r="1176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1176" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1176" s="3" t="s">
         <v>181</v>
       </c>
@@ -29508,7 +29511,7 @@
         <v>38.213999999999999</v>
       </c>
     </row>
-    <row r="1177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1177" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1177" s="3" t="s">
         <v>181</v>
       </c>
@@ -29532,7 +29535,7 @@
         <v>483.53800000000001</v>
       </c>
     </row>
-    <row r="1178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1178" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1178" s="3" t="s">
         <v>186</v>
       </c>
@@ -29556,7 +29559,7 @@
         <v>29.795999999999999</v>
       </c>
     </row>
-    <row r="1179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1179" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1179" s="3" t="s">
         <v>186</v>
       </c>
@@ -29580,7 +29583,7 @@
         <v>81.38</v>
       </c>
     </row>
-    <row r="1180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1180" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1180" s="3" t="s">
         <v>186</v>
       </c>
@@ -29604,7 +29607,7 @@
         <v>19.760000000000002</v>
       </c>
     </row>
-    <row r="1181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1181" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1181" s="3" t="s">
         <v>186</v>
       </c>
@@ -29628,7 +29631,7 @@
         <v>71.13600000000001</v>
       </c>
     </row>
-    <row r="1182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1182" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1182" s="3" t="s">
         <v>186</v>
       </c>
@@ -29652,7 +29655,7 @@
         <v>242.68799999999999</v>
       </c>
     </row>
-    <row r="1183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1183" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1183" s="3" t="s">
         <v>186</v>
       </c>
@@ -29676,7 +29679,7 @@
         <v>489.06239999999997</v>
       </c>
     </row>
-    <row r="1184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1184" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1184" s="3" t="s">
         <v>186</v>
       </c>
@@ -29700,7 +29703,7 @@
         <v>114.3296</v>
       </c>
     </row>
-    <row r="1185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1185" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1185" s="3" t="s">
         <v>256</v>
       </c>
@@ -29724,7 +29727,7 @@
         <v>544.25840000000005</v>
       </c>
     </row>
-    <row r="1186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1186" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1186" s="3" t="s">
         <v>256</v>
       </c>
@@ -29748,7 +29751,7 @@
         <v>206.63160000000002</v>
       </c>
     </row>
-    <row r="1187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1187" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1187" s="3" t="s">
         <v>256</v>
       </c>
@@ -29772,7 +29775,7 @@
         <v>50.741600000000005</v>
       </c>
     </row>
-    <row r="1188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1188" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1188" s="3" t="s">
         <v>256</v>
       </c>
@@ -29796,7 +29799,7 @@
         <v>133.4606</v>
       </c>
     </row>
-    <row r="1189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1189" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1189" s="3" t="s">
         <v>256</v>
       </c>
@@ -29820,7 +29823,7 @@
         <v>191.29390000000001</v>
       </c>
     </row>
-    <row r="1190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1190" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1190" s="3" t="s">
         <v>256</v>
       </c>
@@ -29844,7 +29847,7 @@
         <v>226.90920000000003</v>
       </c>
     </row>
-    <row r="1191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1191" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1191" s="3" t="s">
         <v>256</v>
       </c>
@@ -29868,7 +29871,7 @@
         <v>208.54400000000001</v>
       </c>
     </row>
-    <row r="1192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1192" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1192" s="3" t="s">
         <v>256</v>
       </c>
@@ -29892,7 +29895,7 @@
         <v>309.51830000000001</v>
       </c>
     </row>
-    <row r="1193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1193" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1193" s="3" t="s">
         <v>256</v>
       </c>
@@ -29916,7 +29919,7 @@
         <v>302.59320000000002</v>
       </c>
     </row>
-    <row r="1194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1194" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1194" s="3" t="s">
         <v>256</v>
       </c>
@@ -29940,7 +29943,7 @@
         <v>400.9796</v>
       </c>
     </row>
-    <row r="1195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1195" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1195" s="3" t="s">
         <v>256</v>
       </c>
@@ -29964,11 +29967,3659 @@
         <v>215.649</v>
       </c>
     </row>
+    <row r="1196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1196" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1196" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1196" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1196" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1196" s="2">
+        <v>556.4</v>
+      </c>
+      <c r="F1196" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1196" s="2">
+        <f t="shared" si="15"/>
+        <v>55.64</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1197" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1197" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1197" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1197" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1197" s="2">
+        <v>2684.16</v>
+      </c>
+      <c r="F1197" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1197" s="2">
+        <f t="shared" si="15"/>
+        <v>268.416</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1198" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1198" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1198" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1198" s="2">
+        <v>182.4</v>
+      </c>
+      <c r="F1198" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1198" s="2">
+        <f t="shared" si="15"/>
+        <v>18.240000000000002</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1199" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1199" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1199" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1199" s="2">
+        <v>5458.56</v>
+      </c>
+      <c r="F1199" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1199" s="2">
+        <f t="shared" si="15"/>
+        <v>545.85600000000011</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1200" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1200" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1200" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1200" s="2">
+        <v>158.72</v>
+      </c>
+      <c r="F1200" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1200" s="2">
+        <f t="shared" si="15"/>
+        <v>15.872</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1201" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1201" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1201" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1201" s="2">
+        <v>2533.6999999999998</v>
+      </c>
+      <c r="F1201" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1201" s="2">
+        <f t="shared" si="15"/>
+        <v>253.37</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1202" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1202" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1202" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1202" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1202" s="2">
+        <v>145.91999999999999</v>
+      </c>
+      <c r="F1202" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1202" s="2">
+        <f t="shared" si="15"/>
+        <v>14.591999999999999</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1203" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1203" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1203" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1203" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1203" s="2">
+        <v>1321.25</v>
+      </c>
+      <c r="F1203" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1203" s="2">
+        <f t="shared" si="15"/>
+        <v>132.125</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1204" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1204" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1204" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1204" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1204" s="2">
+        <v>949.12</v>
+      </c>
+      <c r="F1204" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1204" s="2">
+        <f t="shared" si="15"/>
+        <v>94.912000000000006</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1205" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1205" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1205" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1205" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1205" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1205" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1205" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1206" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1206" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C1206" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1206" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1206" s="2">
+        <v>350.55</v>
+      </c>
+      <c r="F1206" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1206" s="2">
+        <f t="shared" si="15"/>
+        <v>35.055</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1207" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1207" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1207" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1207" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1207" s="2">
+        <v>11625.82</v>
+      </c>
+      <c r="F1207" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1207" s="2">
+        <f t="shared" si="15"/>
+        <v>1162.5820000000001</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1208" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1208" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1208" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1208" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1208" s="2">
+        <v>7015.68</v>
+      </c>
+      <c r="F1208" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1208" s="2">
+        <f t="shared" si="15"/>
+        <v>561.25440000000003</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1209" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1209" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1209" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1209" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1209" s="2">
+        <v>6308.48</v>
+      </c>
+      <c r="F1209" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1209" s="2">
+        <f t="shared" si="15"/>
+        <v>504.67839999999995</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1210" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1210" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1210" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D1210" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1210" s="2">
+        <v>2782.72</v>
+      </c>
+      <c r="F1210" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1210" s="2">
+        <f t="shared" si="15"/>
+        <v>222.61759999999998</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1211" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1211" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1211" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D1211" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1211" s="2">
+        <v>1916.8</v>
+      </c>
+      <c r="F1211" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1211" s="2">
+        <f t="shared" si="15"/>
+        <v>153.34399999999999</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1212" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1212" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1212" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D1212" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1212" s="2">
+        <v>1662.72</v>
+      </c>
+      <c r="F1212" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1212" s="2">
+        <f t="shared" si="15"/>
+        <v>133.01760000000002</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1213" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1213" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1213" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1213" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1213" s="2">
+        <v>1790.88</v>
+      </c>
+      <c r="F1213" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1213" s="2">
+        <f t="shared" si="15"/>
+        <v>143.27040000000002</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1214" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1214" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1214" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1214" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1214" s="2">
+        <v>2607.8000000000002</v>
+      </c>
+      <c r="F1214" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1214" s="2">
+        <f t="shared" si="15"/>
+        <v>208.62400000000002</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1215" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1215" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1215" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D1215" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1215" s="2">
+        <v>2676.48</v>
+      </c>
+      <c r="F1215" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1215" s="2">
+        <f t="shared" si="15"/>
+        <v>214.11840000000001</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1216" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1216" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1216" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D1216" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1216" s="2">
+        <v>5457.68</v>
+      </c>
+      <c r="F1216" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1216" s="2">
+        <f t="shared" si="15"/>
+        <v>436.61440000000005</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1217" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1217" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1217" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1217" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1217" s="2">
+        <v>2273.4</v>
+      </c>
+      <c r="F1217" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1217" s="2">
+        <f t="shared" si="15"/>
+        <v>181.87200000000001</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1218" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1218" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1218" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1218" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1218" s="2">
+        <v>689.04</v>
+      </c>
+      <c r="F1218" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1218" s="2">
+        <f t="shared" si="15"/>
+        <v>55.123199999999997</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1219" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1219" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1219" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1219" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1219" s="2">
+        <v>429</v>
+      </c>
+      <c r="F1219" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1219" s="2">
+        <f t="shared" si="15"/>
+        <v>34.32</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1220" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1220" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1220" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1220" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1220" s="2">
+        <v>772.81</v>
+      </c>
+      <c r="F1220" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1220" s="2">
+        <f t="shared" si="15"/>
+        <v>61.824799999999996</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1221" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1221" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1221" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1221" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1221" s="2">
+        <v>248.15</v>
+      </c>
+      <c r="F1221" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1221" s="2">
+        <f t="shared" si="15"/>
+        <v>19.852</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1222" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1222" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1222" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1222" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1222" s="2">
+        <v>1294.92</v>
+      </c>
+      <c r="F1222" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1222" s="2">
+        <f t="shared" si="15"/>
+        <v>103.59360000000001</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1223" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1223" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1223" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1223" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1223" s="2">
+        <v>1273.1400000000001</v>
+      </c>
+      <c r="F1223" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1223" s="2">
+        <f t="shared" si="15"/>
+        <v>101.85120000000001</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1224" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1224" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1224" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D1224" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1224" s="2">
+        <v>295.68</v>
+      </c>
+      <c r="F1224" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1224" s="2">
+        <f t="shared" si="15"/>
+        <v>23.654400000000003</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1225" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1225" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1225" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D1225" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1225" s="2">
+        <v>144.05000000000001</v>
+      </c>
+      <c r="F1225" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1225" s="2">
+        <f t="shared" si="15"/>
+        <v>11.524000000000001</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1226" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1226" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1226" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D1226" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1226" s="2">
+        <v>490.57</v>
+      </c>
+      <c r="F1226" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1226" s="2">
+        <f t="shared" si="15"/>
+        <v>39.245600000000003</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1227" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1227" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1227" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1227" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1227" s="2">
+        <v>276.04000000000002</v>
+      </c>
+      <c r="F1227" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1227" s="2">
+        <f t="shared" si="15"/>
+        <v>22.083200000000001</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1228" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1228" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1228" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1228" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1228" s="2">
+        <v>295.68</v>
+      </c>
+      <c r="F1228" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1228" s="2">
+        <f t="shared" si="15"/>
+        <v>23.654400000000003</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1229" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1229" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1229" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1229" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1229" s="2">
+        <v>420.76</v>
+      </c>
+      <c r="F1229" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1229" s="2">
+        <f t="shared" si="15"/>
+        <v>33.660800000000002</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1230" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1230" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1230" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1230" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1230" s="2">
+        <v>795.29</v>
+      </c>
+      <c r="F1230" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1230" s="2">
+        <f t="shared" si="15"/>
+        <v>63.623199999999997</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1231" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1231" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1231" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1231" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1231" s="2">
+        <v>621.76</v>
+      </c>
+      <c r="F1231" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1231" s="2">
+        <f t="shared" si="15"/>
+        <v>49.7408</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1232" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1232" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1232" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1232" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1232" s="2">
+        <v>1613.04</v>
+      </c>
+      <c r="F1232" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1232" s="2">
+        <f t="shared" si="15"/>
+        <v>129.04320000000001</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1233" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1233" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1233" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1233" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1233" s="2">
+        <v>1284.3599999999999</v>
+      </c>
+      <c r="F1233" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1233" s="2">
+        <f t="shared" si="15"/>
+        <v>102.74879999999999</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1234" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1234" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1234" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1234" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1234" s="2">
+        <v>4065.92</v>
+      </c>
+      <c r="F1234" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1234" s="2">
+        <f t="shared" si="15"/>
+        <v>203.29600000000002</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1235" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1235" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1235" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1235" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1235" s="2">
+        <v>2585.0500000000002</v>
+      </c>
+      <c r="F1235" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1235" s="2">
+        <f t="shared" si="15"/>
+        <v>129.25250000000003</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1236" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1236" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1236" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1236" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1236" s="2">
+        <v>3386.73</v>
+      </c>
+      <c r="F1236" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1236" s="2">
+        <f t="shared" si="15"/>
+        <v>169.3365</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1237" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1237" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1237" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1237" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1237" s="2">
+        <v>3324.78</v>
+      </c>
+      <c r="F1237" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1237" s="2">
+        <f t="shared" si="15"/>
+        <v>166.23900000000003</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1238" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1238" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1238" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1238" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1238" s="2">
+        <v>1795.84</v>
+      </c>
+      <c r="F1238" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1238" s="2">
+        <f t="shared" si="15"/>
+        <v>89.792000000000002</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1239" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1239" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1239" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D1239" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1239" s="2">
+        <v>1935.27</v>
+      </c>
+      <c r="F1239" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1239" s="2">
+        <f t="shared" si="15"/>
+        <v>96.763500000000008</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1240" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1240" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1240" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1240" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1240" s="2">
+        <v>3029.76</v>
+      </c>
+      <c r="F1240" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1240" s="2">
+        <f t="shared" si="15"/>
+        <v>151.48800000000003</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1241" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1241" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1241" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1241" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1241" s="2">
+        <v>2604.5500000000002</v>
+      </c>
+      <c r="F1241" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1241" s="2">
+        <f t="shared" si="15"/>
+        <v>130.22750000000002</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1242" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1242" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1242" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1242" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1242" s="2">
+        <v>4434.54</v>
+      </c>
+      <c r="F1242" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1242" s="2">
+        <f t="shared" si="15"/>
+        <v>221.727</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1243" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1243" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1243" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1243" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1243" s="2">
+        <v>1975.5</v>
+      </c>
+      <c r="F1243" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1243" s="2">
+        <f t="shared" si="15"/>
+        <v>98.775000000000006</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1244" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1244" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1244" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1244" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1244" s="2">
+        <v>10522.88</v>
+      </c>
+      <c r="F1244" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1244" s="2">
+        <f t="shared" si="15"/>
+        <v>526.14400000000001</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1245" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1245" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1245" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1245" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1245" s="2">
+        <v>4894.08</v>
+      </c>
+      <c r="F1245" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1245" s="2">
+        <f t="shared" si="15"/>
+        <v>244.70400000000001</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1246" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1246" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1246" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1246" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1246" s="2">
+        <v>7842.25</v>
+      </c>
+      <c r="F1246" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1246" s="2">
+        <f t="shared" si="15"/>
+        <v>392.11250000000001</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1247" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1247" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1247" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D1247" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1247" s="2">
+        <v>3182.1</v>
+      </c>
+      <c r="F1247" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1247" s="2">
+        <f t="shared" si="15"/>
+        <v>159.10500000000002</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1248" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1248" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1248" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1248" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1248" s="2">
+        <v>820.95</v>
+      </c>
+      <c r="F1248" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1248" s="2">
+        <f t="shared" si="15"/>
+        <v>41.047500000000007</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1249" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1249" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1249" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1249" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1249" s="2">
+        <v>892.54</v>
+      </c>
+      <c r="F1249" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1249" s="2">
+        <f t="shared" si="15"/>
+        <v>44.627000000000002</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1250" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1250" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1250" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1250" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1250" s="2">
+        <v>5049.2</v>
+      </c>
+      <c r="F1250" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1250" s="2">
+        <f t="shared" si="15"/>
+        <v>252.46</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1251" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1251" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1251" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1251" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1251" s="2">
+        <v>572.16</v>
+      </c>
+      <c r="F1251" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1251" s="2">
+        <f t="shared" si="15"/>
+        <v>28.608000000000001</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1252" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1252" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1252" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1252" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1252" s="2">
+        <v>5170.5600000000004</v>
+      </c>
+      <c r="F1252" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1252" s="2">
+        <f t="shared" si="15"/>
+        <v>258.52800000000002</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1253" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1253" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1253" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1253" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1253" s="2">
+        <v>9201.92</v>
+      </c>
+      <c r="F1253" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1253" s="2">
+        <f t="shared" si="15"/>
+        <v>460.096</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1254" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1254" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1254" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D1254" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1254" s="2">
+        <v>172.16</v>
+      </c>
+      <c r="F1254" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1254" s="2">
+        <f t="shared" si="15"/>
+        <v>8.6080000000000005</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1255" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1255" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1255" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D1255" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1255" s="2">
+        <v>960.64</v>
+      </c>
+      <c r="F1255" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1255" s="2">
+        <f t="shared" si="15"/>
+        <v>48.032000000000004</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1256" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1256" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1256" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D1256" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1256" s="2">
+        <v>4542.08</v>
+      </c>
+      <c r="F1256" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1256" s="2">
+        <f t="shared" si="15"/>
+        <v>227.10400000000001</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1257" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1257" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1257" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D1257" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1257" s="2">
+        <v>4782.08</v>
+      </c>
+      <c r="F1257" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1257" s="2">
+        <f t="shared" si="15"/>
+        <v>239.10400000000001</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1258" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1258" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1258" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1258" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1258" s="2">
+        <v>7129.6</v>
+      </c>
+      <c r="F1258" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1258" s="2">
+        <f t="shared" si="15"/>
+        <v>356.48</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1259" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1259" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C1259" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1259" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1259" s="2">
+        <v>7697.3</v>
+      </c>
+      <c r="F1259" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1259" s="2">
+        <f t="shared" si="15"/>
+        <v>384.86500000000001</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1260" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1260" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1260" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="D1260" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1260" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1260" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1260" s="2">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1261" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1261" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1261" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1261" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1261" s="2">
+        <v>2760.55</v>
+      </c>
+      <c r="F1261" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="G1261" s="2">
+        <f t="shared" si="15"/>
+        <v>138.0275</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1262" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1262" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1262" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1262" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1262" s="2">
+        <v>5701.58</v>
+      </c>
+      <c r="F1262" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1262" s="2">
+        <f t="shared" si="15"/>
+        <v>456.12639999999999</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1263" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1263" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1263" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1263" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1263" s="2">
+        <v>238.68</v>
+      </c>
+      <c r="F1263" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1263" s="2">
+        <f t="shared" si="15"/>
+        <v>19.0944</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1264" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1264" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1264" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1264" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1264" s="2">
+        <v>267.3</v>
+      </c>
+      <c r="F1264" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1264" s="2">
+        <f t="shared" si="15"/>
+        <v>21.384</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1265" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1265" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1265" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1265" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1265" s="2">
+        <v>869.94</v>
+      </c>
+      <c r="F1265" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1265" s="2">
+        <f t="shared" si="15"/>
+        <v>69.595200000000006</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1266" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1266" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1266" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1266" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1266" s="2">
+        <v>370.44</v>
+      </c>
+      <c r="F1266" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1266" s="2">
+        <f t="shared" si="15"/>
+        <v>29.635200000000001</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1267" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1267" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1267" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1267" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1267" s="2">
+        <v>1432.96</v>
+      </c>
+      <c r="F1267" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1267" s="2">
+        <f t="shared" si="15"/>
+        <v>114.63680000000001</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1268" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1268" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1268" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1268" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1268" s="2">
+        <v>1320.66</v>
+      </c>
+      <c r="F1268" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1268" s="2">
+        <f t="shared" si="15"/>
+        <v>105.65280000000001</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1269" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1269" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1269" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1269" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1269" s="2">
+        <v>4458.24</v>
+      </c>
+      <c r="F1269" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1269" s="2">
+        <f t="shared" si="15"/>
+        <v>356.6592</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1270" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1270" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1270" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D1270" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1270" s="2">
+        <v>1215.72</v>
+      </c>
+      <c r="F1270" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1270" s="2">
+        <f t="shared" si="15"/>
+        <v>97.257600000000011</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1271" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1271" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1271" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1271" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1271" s="2">
+        <v>669.9</v>
+      </c>
+      <c r="F1271" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1271" s="2">
+        <f t="shared" si="15"/>
+        <v>53.591999999999999</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1272" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1272" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1272" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1272" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1272" s="2">
+        <v>7014.5</v>
+      </c>
+      <c r="F1272" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1272" s="2">
+        <f t="shared" si="15"/>
+        <v>561.16</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1273" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1273" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1273" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1273" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1273" s="2">
+        <v>10817.41</v>
+      </c>
+      <c r="F1273" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1273" s="2">
+        <f t="shared" si="15"/>
+        <v>865.39279999999997</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1274" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1274" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1274" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1274" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1274" s="2">
+        <v>368.64</v>
+      </c>
+      <c r="F1274" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1274" s="2">
+        <f t="shared" si="15"/>
+        <v>29.491199999999999</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1275" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1275" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1275" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D1275" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1275" s="2">
+        <v>4708.59</v>
+      </c>
+      <c r="F1275" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1275" s="2">
+        <f t="shared" si="15"/>
+        <v>376.68720000000002</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1276" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1276" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1276" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D1276" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1276" s="2">
+        <v>1200.55</v>
+      </c>
+      <c r="F1276" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1276" s="2">
+        <f t="shared" si="15"/>
+        <v>96.043999999999997</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1277" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1277" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1277" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1277" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1277" s="2">
+        <v>6928</v>
+      </c>
+      <c r="F1277" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1277" s="2">
+        <f t="shared" si="15"/>
+        <v>554.24</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1278" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1278" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1278" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1278" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1278" s="2">
+        <v>3546.24</v>
+      </c>
+      <c r="F1278" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1278" s="2">
+        <f t="shared" si="15"/>
+        <v>283.69919999999996</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1279" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1279" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1279" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1279" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1279" s="2">
+        <v>4965.76</v>
+      </c>
+      <c r="F1279" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1279" s="2">
+        <f t="shared" si="15"/>
+        <v>397.26080000000002</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1280" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1280" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1280" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1280" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1280" s="2">
+        <v>2338.4</v>
+      </c>
+      <c r="F1280" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1280" s="2">
+        <f t="shared" si="15"/>
+        <v>187.072</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1281" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1281" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1281" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1281" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1281" s="2">
+        <v>103.68</v>
+      </c>
+      <c r="F1281" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1281" s="2">
+        <f t="shared" si="15"/>
+        <v>8.2944000000000013</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1282" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1282" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1282" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D1282" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1282" s="2">
+        <v>711.72</v>
+      </c>
+      <c r="F1282" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1282" s="2">
+        <f t="shared" si="15"/>
+        <v>56.937600000000003</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1283" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1283" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1283" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1283" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1283" s="2">
+        <v>3408.48</v>
+      </c>
+      <c r="F1283" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1283" s="2">
+        <f t="shared" si="15"/>
+        <v>272.67840000000001</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1284" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1284" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1284" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1284" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1284" s="2">
+        <v>612.48</v>
+      </c>
+      <c r="F1284" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1284" s="2">
+        <f t="shared" si="15"/>
+        <v>48.998400000000004</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1285" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1285" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1285" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1285" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1285" s="2">
+        <v>4883.2</v>
+      </c>
+      <c r="F1285" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1285" s="2">
+        <f t="shared" si="15"/>
+        <v>390.65600000000001</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1286" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1286" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1286" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1286" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1286" s="2">
+        <v>330.72</v>
+      </c>
+      <c r="F1286" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1286" s="2">
+        <f t="shared" ref="G1286:G1347" si="16">E1286*F1286</f>
+        <v>26.457600000000003</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1287" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1287" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1287" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1287" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1287" s="2">
+        <v>2099.84</v>
+      </c>
+      <c r="F1287" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1287" s="2">
+        <f t="shared" si="16"/>
+        <v>167.9872</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1288" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1288" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1288" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1288" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1288" s="2">
+        <v>110.84</v>
+      </c>
+      <c r="F1288" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1288" s="2">
+        <f t="shared" si="16"/>
+        <v>8.8672000000000004</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1289" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1289" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1289" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1289" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1289" s="2">
+        <v>70.72</v>
+      </c>
+      <c r="F1289" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1289" s="2">
+        <f t="shared" si="16"/>
+        <v>5.6576000000000004</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1290" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1290" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1290" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1290" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1290" s="2">
+        <v>9869.61</v>
+      </c>
+      <c r="F1290" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1290" s="2">
+        <f t="shared" si="16"/>
+        <v>986.96100000000013</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1291" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1291" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1291" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1291" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1291" s="2">
+        <v>1750.95</v>
+      </c>
+      <c r="F1291" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1291" s="2">
+        <f t="shared" si="16"/>
+        <v>175.09500000000003</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1292" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1292" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1292" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D1292" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1292" s="2">
+        <v>5448.6</v>
+      </c>
+      <c r="F1292" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1292" s="2">
+        <f t="shared" si="16"/>
+        <v>544.86</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1293" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1293" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1293" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D1293" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1293" s="2">
+        <v>153.4</v>
+      </c>
+      <c r="F1293" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1293" s="2">
+        <f t="shared" si="16"/>
+        <v>15.340000000000002</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1294" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1294" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1294" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1294" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1294" s="2">
+        <v>3232</v>
+      </c>
+      <c r="F1294" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1294" s="2">
+        <f t="shared" si="16"/>
+        <v>323.20000000000005</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1295" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1295" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1295" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1295" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1295" s="2">
+        <v>7029.75</v>
+      </c>
+      <c r="F1295" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1295" s="2">
+        <f t="shared" si="16"/>
+        <v>702.97500000000002</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1296" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1296" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1296" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1296" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1296" s="2">
+        <v>622.72</v>
+      </c>
+      <c r="F1296" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1296" s="2">
+        <f t="shared" si="16"/>
+        <v>62.272000000000006</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1297" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1297" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1297" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D1297" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1297" s="2">
+        <v>1052.8</v>
+      </c>
+      <c r="F1297" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1297" s="2">
+        <f t="shared" si="16"/>
+        <v>105.28</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1298" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1298" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1298" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D1298" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1298" s="2">
+        <v>1598.72</v>
+      </c>
+      <c r="F1298" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1298" s="2">
+        <f t="shared" si="16"/>
+        <v>159.87200000000001</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1299" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1299" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1299" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1299" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1299" s="2">
+        <v>1614.08</v>
+      </c>
+      <c r="F1299" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1299" s="2">
+        <f t="shared" si="16"/>
+        <v>161.40800000000002</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1300" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1300" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C1300" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1300" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1300" s="2">
+        <v>0</v>
+      </c>
+      <c r="F1300" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1300" s="2">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1301" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1301" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1301" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1301" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1301" s="2">
+        <v>2937.66</v>
+      </c>
+      <c r="F1301" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1301" s="2">
+        <f t="shared" si="16"/>
+        <v>293.76600000000002</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1302" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1302" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1302" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1302" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1302" s="2">
+        <v>6286.08</v>
+      </c>
+      <c r="F1302" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1302" s="2">
+        <f t="shared" si="16"/>
+        <v>628.60800000000006</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1303" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1303" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1303" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1303" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1303" s="2">
+        <v>2967.04</v>
+      </c>
+      <c r="F1303" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1303" s="2">
+        <f t="shared" si="16"/>
+        <v>296.70400000000001</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1304" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1304" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1304" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D1304" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1304" s="2">
+        <v>10187.52</v>
+      </c>
+      <c r="F1304" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1304" s="2">
+        <f t="shared" si="16"/>
+        <v>1018.7520000000001</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1305" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1305" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C1305" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D1305" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1305" s="2">
+        <v>3850.16</v>
+      </c>
+      <c r="F1305" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1305" s="2">
+        <f t="shared" si="16"/>
+        <v>385.01600000000002</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1306" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1306" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1306" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1306" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1306" s="2">
+        <v>1345.74</v>
+      </c>
+      <c r="F1306" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1306" s="2">
+        <f t="shared" si="16"/>
+        <v>134.57400000000001</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1307" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1307" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1307" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D1307" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1307" s="2">
+        <v>1261.7</v>
+      </c>
+      <c r="F1307" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1307" s="2">
+        <f t="shared" si="16"/>
+        <v>126.17000000000002</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1308" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1308" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1308" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1308" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1308" s="2">
+        <v>2605.86</v>
+      </c>
+      <c r="F1308" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1308" s="2">
+        <f t="shared" si="16"/>
+        <v>260.58600000000001</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1309" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1309" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C1309" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1309" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1309" s="2">
+        <v>3178.12</v>
+      </c>
+      <c r="F1309" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1309" s="2">
+        <f t="shared" si="16"/>
+        <v>317.81200000000001</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1310" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1310" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1310" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1310" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1310" s="2">
+        <v>4094.75</v>
+      </c>
+      <c r="F1310" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1310" s="2">
+        <f t="shared" si="16"/>
+        <v>409.47500000000002</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1311" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1311" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1311" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1311" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1311" s="2">
+        <v>2272.4899999999998</v>
+      </c>
+      <c r="F1311" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1311" s="2">
+        <f t="shared" si="16"/>
+        <v>227.249</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1312" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1312" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1312" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1312" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1312" s="2">
+        <v>4224.66</v>
+      </c>
+      <c r="F1312" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1312" s="2">
+        <f t="shared" si="16"/>
+        <v>422.46600000000001</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1313" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1313" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1313" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1313" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1313" s="2">
+        <v>3329.28</v>
+      </c>
+      <c r="F1313" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1313" s="2">
+        <f t="shared" si="16"/>
+        <v>332.92800000000005</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1314" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1314" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1314" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1314" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1314" s="2">
+        <v>195.36</v>
+      </c>
+      <c r="F1314" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1314" s="2">
+        <f t="shared" si="16"/>
+        <v>19.536000000000001</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1315" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1315" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1315" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1315" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1315" s="2">
+        <v>13394.19</v>
+      </c>
+      <c r="F1315" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1315" s="2">
+        <f t="shared" si="16"/>
+        <v>1339.4190000000001</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1316" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1316" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1316" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1316" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1316" s="2">
+        <v>8487.7000000000007</v>
+      </c>
+      <c r="F1316" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1316" s="2">
+        <f t="shared" si="16"/>
+        <v>848.7700000000001</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1317" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1317" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1317" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D1317" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1317" s="2">
+        <v>1276</v>
+      </c>
+      <c r="F1317" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1317" s="2">
+        <f t="shared" si="16"/>
+        <v>127.60000000000001</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1318" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1318" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C1318" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1318" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1318" s="2">
+        <v>3770.8</v>
+      </c>
+      <c r="F1318" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1318" s="2">
+        <f t="shared" si="16"/>
+        <v>377.08000000000004</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1319" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1319" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C1319" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D1319" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1319" s="2">
+        <v>3073.62</v>
+      </c>
+      <c r="F1319" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1319" s="2">
+        <f t="shared" si="16"/>
+        <v>307.36200000000002</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1320" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1320" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1320" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D1320" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1320" s="2">
+        <v>5612.76</v>
+      </c>
+      <c r="F1320" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1320" s="2">
+        <f t="shared" si="16"/>
+        <v>561.27600000000007</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1321" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1321" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1321" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D1321" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1321" s="2">
+        <v>2354.56</v>
+      </c>
+      <c r="F1321" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1321" s="2">
+        <f t="shared" si="16"/>
+        <v>235.45600000000002</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1322" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1322" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C1322" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D1322" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1322" s="2">
+        <v>2401.4699999999998</v>
+      </c>
+      <c r="F1322" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1322" s="2">
+        <f t="shared" si="16"/>
+        <v>240.14699999999999</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1323" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1323" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C1323" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1323" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1323" s="2">
+        <v>2534.4</v>
+      </c>
+      <c r="F1323" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1323" s="2">
+        <f t="shared" si="16"/>
+        <v>253.44000000000003</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1324" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1324" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1324" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1324" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1324" s="2">
+        <v>1534</v>
+      </c>
+      <c r="F1324" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1324" s="2">
+        <f t="shared" si="16"/>
+        <v>153.4</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1325" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1325" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1325" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D1325" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1325" s="2">
+        <v>678.28</v>
+      </c>
+      <c r="F1325" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1325" s="2">
+        <f t="shared" si="16"/>
+        <v>67.828000000000003</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1326" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1326" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1326" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1326" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1326" s="2">
+        <v>473.68</v>
+      </c>
+      <c r="F1326" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1326" s="2">
+        <f t="shared" si="16"/>
+        <v>47.368000000000002</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1327" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1327" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1327" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1327" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1327" s="2">
+        <v>328.68</v>
+      </c>
+      <c r="F1327" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1327" s="2">
+        <f t="shared" si="16"/>
+        <v>32.868000000000002</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1328" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B1328" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1328" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1328" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1328" s="2">
+        <v>4769.04</v>
+      </c>
+      <c r="F1328" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1328" s="2">
+        <f t="shared" si="16"/>
+        <v>476.904</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1329" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1329" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1329" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D1329" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1329" s="2">
+        <v>405.6</v>
+      </c>
+      <c r="F1329" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1329" s="2">
+        <f t="shared" si="16"/>
+        <v>32.448</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1330" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1330" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1330" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1330" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1330" s="2">
+        <v>1238.9000000000001</v>
+      </c>
+      <c r="F1330" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1330" s="2">
+        <f t="shared" si="16"/>
+        <v>99.112000000000009</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1331" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1331" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1331" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D1331" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1331" s="2">
+        <v>271.7</v>
+      </c>
+      <c r="F1331" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1331" s="2">
+        <f t="shared" si="16"/>
+        <v>21.736000000000001</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1332" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1332" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1332" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1332" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1332" s="2">
+        <v>956.8</v>
+      </c>
+      <c r="F1332" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1332" s="2">
+        <f t="shared" si="16"/>
+        <v>76.543999999999997</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1333" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1333" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1333" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1333" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1333" s="2">
+        <v>3087.36</v>
+      </c>
+      <c r="F1333" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1333" s="2">
+        <f t="shared" si="16"/>
+        <v>246.98880000000003</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1334" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1334" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1334" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D1334" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1334" s="2">
+        <v>7735.04</v>
+      </c>
+      <c r="F1334" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1334" s="2">
+        <f t="shared" si="16"/>
+        <v>618.80320000000006</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1335" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1335" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1335" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1335" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1335" s="2">
+        <v>538.24</v>
+      </c>
+      <c r="F1335" s="1">
+        <v>0.08</v>
+      </c>
+      <c r="G1335" s="2">
+        <f t="shared" si="16"/>
+        <v>43.059200000000004</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1336" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1336" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1336" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1336" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1336" s="2">
+        <v>9870.2000000000007</v>
+      </c>
+      <c r="F1336" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1336" s="2">
+        <f t="shared" si="16"/>
+        <v>690.9140000000001</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1337" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1337" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1337" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1337" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1337" s="2">
+        <v>3157.92</v>
+      </c>
+      <c r="F1337" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1337" s="2">
+        <f t="shared" si="16"/>
+        <v>221.05440000000002</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1338" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1338" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1338" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1338" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1338" s="2">
+        <v>697</v>
+      </c>
+      <c r="F1338" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1338" s="2">
+        <f t="shared" si="16"/>
+        <v>48.790000000000006</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1339" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1339" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1339" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1339" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1339" s="2">
+        <v>2511.92</v>
+      </c>
+      <c r="F1339" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1339" s="2">
+        <f t="shared" si="16"/>
+        <v>175.83440000000002</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1340" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1340" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1340" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D1340" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1340" s="2">
+        <v>3077</v>
+      </c>
+      <c r="F1340" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1340" s="2">
+        <f t="shared" si="16"/>
+        <v>215.39000000000001</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1341" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1341" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1341" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1341" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1341" s="2">
+        <v>3366</v>
+      </c>
+      <c r="F1341" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1341" s="2">
+        <f t="shared" si="16"/>
+        <v>235.62000000000003</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1342" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1342" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1342" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D1342" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1342" s="2">
+        <v>3243.8</v>
+      </c>
+      <c r="F1342" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1342" s="2">
+        <f t="shared" si="16"/>
+        <v>227.06600000000003</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1343" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1343" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1343" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D1343" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1343" s="2">
+        <v>5414.5</v>
+      </c>
+      <c r="F1343" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1343" s="2">
+        <f t="shared" si="16"/>
+        <v>379.01500000000004</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1344" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1344" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1344" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D1344" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1344" s="2">
+        <v>4104.4799999999996</v>
+      </c>
+      <c r="F1344" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1344" s="2">
+        <f t="shared" si="16"/>
+        <v>287.31360000000001</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1345" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1345" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1345" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1345" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1345" s="2">
+        <v>5773.72</v>
+      </c>
+      <c r="F1345" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1345" s="2">
+        <f t="shared" si="16"/>
+        <v>404.16040000000004</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1346" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1346" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1346" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D1346" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1346" s="2">
+        <v>4082.72</v>
+      </c>
+      <c r="F1346" s="1">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G1346" s="2">
+        <f t="shared" si="16"/>
+        <v>285.79040000000003</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1347" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B1347" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1347" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1347" s="9">
+        <v>46235</v>
+      </c>
+      <c r="E1347" s="2">
+        <v>3642.6</v>
+      </c>
+      <c r="F1347" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="G1347" s="2">
+        <f t="shared" si="16"/>
+        <v>364.26</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G1195" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:G1347" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="3">
       <filters>
-        <dateGroupItem year="2026" month="7" dateTimeGrouping="month"/>
+        <dateGroupItem year="2026" month="8" dateTimeGrouping="month"/>
       </filters>
     </filterColumn>
   </autoFilter>
